--- a/sources/forest_step9.xlsx
+++ b/sources/forest_step9.xlsx
@@ -7650,11 +7650,6 @@
           <t>Somersault will juggle on a hit if the previous kicks were blocked or whiffed.</t>
         </is>
       </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="Z81" t="inlineStr">
         <is>
           <t>b016ecd3-0a86-41a2-9980-d1a929f89109</t>
@@ -7896,11 +7891,6 @@
           <t>Somersault will juggle on a hit if the previous kicks were blocked or whiffed.</t>
         </is>
       </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="Z84" t="inlineStr">
         <is>
           <t>66166acc-0611-4ca1-860e-c1073bb9d1e8</t>
@@ -8797,11 +8787,6 @@
       <c r="X93" t="inlineStr">
         <is>
           <t>Somersault will juggle on a hit if the previous kicks were blocked or whiffed.</t>
-        </is>
-      </c>
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">

--- a/sources/forest_step9.xlsx
+++ b/sources/forest_step9.xlsx
@@ -4987,22 +4987,27 @@
     <row r="56">
       <c r="B56" t="inlineStr">
         <is>
-          <t>– ~4 [~D]</t>
+          <t>– ~4</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>db+2 ~4 [~D]</t>
+          <t>db+2 ~4</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>– Spring Kick [PLD]</t>
+          <t>– Spring Kick</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dragon Whip – Spring Kick [PLD]</t>
+          <t>Dragon Whip – Spring Kick</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>(~D)PLD</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -7358,22 +7363,27 @@
     <row r="79">
       <c r="B79" t="inlineStr">
         <is>
-          <t>d+3+4 [~D]</t>
+          <t>d+3+4</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>d+3+4 [~D]</t>
+          <t>d+3+4</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Frog Man [KND]</t>
+          <t>Frog Man</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Frog Man [KND]</t>
+          <t>Frog Man</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>(~D)KND</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">

--- a/sources/forest_step9.xlsx
+++ b/sources/forest_step9.xlsx
@@ -996,6 +996,11 @@
           <t>The initial grab does no damage.</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>c496aa41-bc15-473a-b020-7fdb437577cf</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>c496aa41-bc15-473a-b020-7fdb437577cf</t>
@@ -1063,6 +1068,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>daf033ef-4b67-4b29-86af-e6b2fab70477</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>daf033ef-4b67-4b29-86af-e6b2fab70477</t>
@@ -1125,6 +1135,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>1726e35f-9e18-4c65-a787-332f9f98cc84</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>1726e35f-9e18-4c65-a787-332f9f98cc84</t>
@@ -1185,6 +1200,11 @@
       <c r="V11" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>a1c6311d-6e89-4a3a-b759-44f0ce100eea</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -10453,6 +10473,11 @@
           <t>mhmhhLhhhm</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>3176b347-df34-4e1d-aba7-0986acc47022</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>3176b347-df34-4e1d-aba7-0986acc47022</t>
@@ -10500,6 +10525,11 @@
           <t>mhmhhLmlLm</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>f1b78286-7ba8-4bda-bee5-c8b848d48f48</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>f1b78286-7ba8-4bda-bee5-c8b848d48f48</t>
@@ -10547,6 +10577,11 @@
           <t>mhmhhLmlLm</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>58c32a2c-b1e2-4611-949c-911167465bf7</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>58c32a2c-b1e2-4611-949c-911167465bf7</t>
@@ -10594,6 +10629,11 @@
           <t>mlmhhLhhhm</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>30f18387-0cd0-40f9-bf5b-9602c4d57833</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>30f18387-0cd0-40f9-bf5b-9602c4d57833</t>
@@ -10641,6 +10681,11 @@
           <t>mlmhhLmhlm</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>a1dab966-d331-415b-9775-354f1c4d19a5</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>a1dab966-d331-415b-9775-354f1c4d19a5</t>
@@ -10686,6 +10731,11 @@
       <c r="T121" t="inlineStr">
         <is>
           <t>mlmhhLmlLm</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>99593a10-9a71-4270-8908-8fdf661c902a</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
